--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110074161</v>
+        <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>98016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öjsjön, Sm</t>
+          <t>Krusgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573465</v>
+        <v>573311</v>
       </c>
       <c r="R2" t="n">
-        <v>6448440</v>
+        <v>6448584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett par i sitt häckningsrevir som hotas av avverkning av markägare  Sveaskog.</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,16 +775,350 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137301445</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137305201</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98016</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Öjsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>573302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6448588</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305201</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137301376</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Krusgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573311</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6448584</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137301376</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110074161</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öjsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573465</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6448440</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir som hotas av avverkning av markägare  Sveaskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110074161</t>
         </is>
@@ -796,6 +1127,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37807-2026 artfynd.xlsx
+++ b/artfynd/A 37807-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
